--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstSaleDepartment001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstSaleDepartment001.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13860" windowHeight="2250"/>
@@ -18,18 +18,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
-    <t>营业部代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>营业部名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属券商</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>IP地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -72,13 +60,25 @@
   <si>
     <t>是否净价回报</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柜台代码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柜台名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属经纪商</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +92,11 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,7 +139,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -176,7 +181,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -211,7 +216,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -421,53 +426,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.875" customWidth="1"/>
+    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -480,7 +489,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -490,7 +499,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
